--- a/projetos/OBRA_TMULT/03_PLANEJAMENTO_E_CRONOGRAMA/CRONOGRAMA_FISICO_FINANCEIRO_TMULT.xlsx
+++ b/projetos/OBRA_TMULT/03_PLANEJAMENTO_E_CRONOGRAMA/CRONOGRAMA_FISICO_FINANCEIRO_TMULT.xlsx
@@ -32,7 +32,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -726,7 +726,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EDIFÍCIO ADMINISTRATIVO TMULT (PORTO DO AÇU) — CRONOGRAMA FÍSICO-FINANCEIRO &amp; CURVA S</t>
+          <t>OBRA TMULT — CRONOGRAMA FÍSICO-FINANCEIRO &amp; CURVA S</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linha de Base Oficial 01 (Baseline 01) | Prazo: 6 Meses (26 Semanas / 180 Dias) | Base Orçamentária: SINAPI SP 07/2026 Turnkey</t>
+          <t>Linha de Base Oficial 01 (Baseline 01) | Prazo: 6 Meses (180 Dias) | Base Orçamentária: Turnkey</t>
         </is>
       </c>
     </row>
@@ -944,31 +944,31 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OBRA TMULT — MATRIZ ANALÍTICA DE DISTRIBUIÇÃO MENSAL (158 ITENS DA EAP)</t>
+          <t>TMULT — MATRIZ ANALÍTICA DE DISTRIBUIÇÃO MENSAL (158 ITENS DA EAP)</t>
         </is>
       </c>
     </row>

--- a/projetos/OBRA_TMULT/03_PLANEJAMENTO_E_CRONOGRAMA/CRONOGRAMA_FISICO_FINANCEIRO_TMULT.xlsx
+++ b/projetos/OBRA_TMULT/03_PLANEJAMENTO_E_CRONOGRAMA/CRONOGRAMA_FISICO_FINANCEIRO_TMULT.xlsx
@@ -821,16 +821,16 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>366373.12</v>
+        <v>347328.2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.220605395734301</v>
+        <v>0.2091378183276176</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>807710.99</v>
+        <v>788666.0699999999</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.4863495514842739</v>
+        <v>0.4748819740775905</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.541</v>
@@ -843,16 +843,16 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>245681.39</v>
+        <v>251786.96</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.1479329058461034</v>
+        <v>0.1516092718579808</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1053392.38</v>
+        <v>1040453.03</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.6342824573303772</v>
+        <v>0.6264912459355713</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0.6984999999999999</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>320416.9</v>
+        <v>333356.25</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.1929336328616519</v>
+        <v>0.200724844256458</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>1373809.28</v>
@@ -6088,22 +6088,22 @@
         <v>0</v>
       </c>
       <c r="L75" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="5" t="n">
         <v>8420.219999999999</v>
-      </c>
-      <c r="N75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R75" s="6" t="n">
         <v>0</v>
@@ -6159,22 +6159,22 @@
         <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="8" t="n">
         <v>4519.13</v>
-      </c>
-      <c r="N76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -6230,16 +6230,16 @@
         <v>0</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" s="5" t="n">
         <v>5611.09</v>
-      </c>
-      <c r="N77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="P77" s="6" t="n">
         <v>0</v>
@@ -6301,16 +6301,16 @@
         <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" s="8" t="n">
         <v>494.48</v>
-      </c>
-      <c r="N78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="P78" s="9" t="n">
         <v>0</v>
